--- a/dist/20260926_CoreWeave收支模型_v4_5.xlsx
+++ b/dist/20260926_CoreWeave收支模型_v4_5.xlsx
@@ -44309,7 +44309,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">口徑變更（目標價時點）：基準 </t>
+      <t xml:space="preserve">基準 </t>
     </r>
     <r>
       <rPr>
@@ -44479,7 +44479,109 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">；變動全部來自口徑</t>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(d) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">方法變更（目標價時點改為評價日＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">腿推到同一時點）−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$2.4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（保守 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$1.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、積極 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$1.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
     </r>
   </si>
   <si>
